--- a/Input Excel Sheets/Design Configurations/ASEN4138_ACDesign.xlsx
+++ b/Input Excel Sheets/Design Configurations/ASEN4138_ACDesign.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tyty/Documents/MATLAB/AircraftDesignToolbox-Feb23/MAIN/Input Excel Sheets/Design Configurations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14D1062D-1955-374B-8BAA-112CE1FA03F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B387B404-665E-1149-BF8E-10AD682489A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="1" xr2:uid="{904FC4B5-3CDE-421B-8E98-23A2C72E8C1E}"/>
   </bookViews>
@@ -360,7 +360,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="239">
   <si>
     <t>Length_f</t>
   </si>
@@ -1070,15 +1070,6 @@
     <t>Prop_Dia</t>
   </si>
   <si>
-    <t>B717</t>
-  </si>
-  <si>
-    <t>NACA 64A212</t>
-  </si>
-  <si>
-    <t>NACA 0008</t>
-  </si>
-  <si>
     <t>MD80</t>
   </si>
   <si>
@@ -1086,9 +1077,6 @@
   </si>
   <si>
     <t>NACA 0004</t>
-  </si>
-  <si>
-    <t>BuffAir</t>
   </si>
 </sst>
 </file>
@@ -3168,7 +3156,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28ADD393-55AB-49FB-9382-D2896E9EB980}">
-  <dimension ref="A1:AV15"/>
+  <dimension ref="A1:AV13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="4"/>
@@ -3344,30 +3332,31 @@
         <v>0</v>
       </c>
       <c r="D2" s="4">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="E2" s="4">
-        <v>0.82</v>
+        <v>0.76</v>
       </c>
       <c r="F2" s="4">
-        <v>124</v>
+        <v>147.67060000000001</v>
       </c>
       <c r="G2" s="4">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H2" s="4">
-        <f t="shared" ref="H2:H4" si="0">F2/G2</f>
-        <v>11.272727272727273</v>
+        <f t="shared" ref="H2" si="0">F2/G2</f>
+        <v>9.8447066666666672</v>
       </c>
       <c r="I2" s="4">
-        <f>PI()*(G2/2)^2</f>
-        <v>95.033177771091246</v>
+        <f>0.25*PI()*(G2)^2</f>
+        <v>176.71458676442586</v>
       </c>
       <c r="J2" s="4">
         <v>0</v>
       </c>
       <c r="K2" s="4">
-        <v>4300</v>
+        <f>PI()*G2*F2</f>
+        <v>6958.8130816679532</v>
       </c>
       <c r="L2" s="4">
         <v>1</v>
@@ -3376,43 +3365,45 @@
         <v>1</v>
       </c>
       <c r="N2" s="4">
-        <v>826</v>
+        <v>1209</v>
       </c>
       <c r="O2" s="4">
-        <v>1652</v>
+        <v>2500</v>
       </c>
       <c r="P2" s="4">
-        <v>10.54</v>
+        <f>(107.67717^2)/N2</f>
+        <v>9.5900520588990084</v>
       </c>
       <c r="Q2" s="4">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="R2" s="4">
-        <v>24.5</v>
+        <v>35</v>
       </c>
       <c r="S2" s="4">
-        <v>24.5</v>
+        <v>30</v>
       </c>
       <c r="T2" s="4">
         <v>1.1000000000000001</v>
       </c>
       <c r="U2" s="4">
-        <v>300</v>
+        <v>302.25</v>
       </c>
       <c r="V2" s="4">
-        <v>600</v>
+        <v>620</v>
       </c>
       <c r="W2" s="4">
-        <v>5</v>
+        <v>4.26</v>
       </c>
       <c r="X2" s="4">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="Y2" s="4">
-        <v>25</v>
+        <f>35</f>
+        <v>35</v>
       </c>
       <c r="Z2" s="4">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="AA2" s="4">
         <v>1.1000000000000001</v>
@@ -3439,19 +3430,19 @@
         <v>0</v>
       </c>
       <c r="AI2" s="4">
-        <v>230</v>
+        <v>302.25</v>
       </c>
       <c r="AJ2" s="4">
-        <v>465</v>
+        <v>604.5</v>
       </c>
       <c r="AK2" s="4">
-        <v>1.8</v>
+        <v>4.2622450000000001</v>
       </c>
       <c r="AL2" s="4">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="AM2" s="4">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="AN2" s="4">
         <v>10.5</v>
@@ -3481,313 +3472,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.76</v>
-      </c>
-      <c r="E3" s="4">
-        <v>0.76</v>
-      </c>
-      <c r="F3" s="4">
-        <v>147.67060000000001</v>
-      </c>
-      <c r="G3" s="4">
-        <v>15</v>
-      </c>
-      <c r="H3" s="4">
-        <f t="shared" si="0"/>
-        <v>9.8447066666666672</v>
-      </c>
-      <c r="I3" s="4">
-        <f>0.25*PI()*(G3)^2</f>
-        <v>176.71458676442586</v>
-      </c>
-      <c r="J3" s="4">
-        <v>0</v>
-      </c>
-      <c r="K3" s="4">
-        <f>PI()*G3*F3</f>
-        <v>6958.8130816679532</v>
-      </c>
-      <c r="L3" s="4">
-        <v>1</v>
-      </c>
-      <c r="M3" s="4">
-        <v>1</v>
-      </c>
-      <c r="N3" s="4">
-        <v>1209</v>
-      </c>
-      <c r="O3" s="4">
-        <v>2500</v>
-      </c>
-      <c r="P3" s="4">
-        <f>(107.67717^2)/N3</f>
-        <v>9.5900520588990084</v>
-      </c>
-      <c r="Q3" s="4">
-        <v>0.25</v>
-      </c>
-      <c r="R3" s="4">
-        <v>35</v>
-      </c>
-      <c r="S3" s="4">
-        <v>30</v>
-      </c>
-      <c r="T3" s="4">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="U3" s="4">
-        <f>0.25*N3</f>
-        <v>302.25</v>
-      </c>
-      <c r="V3" s="4">
-        <f>2*U3</f>
-        <v>604.5</v>
-      </c>
-      <c r="W3" s="4">
-        <f>((107.67717/3)^2)/U3</f>
-        <v>4.2622453595106693</v>
-      </c>
-      <c r="X3" s="4">
-        <v>0.4</v>
-      </c>
-      <c r="Y3" s="4">
-        <f>35</f>
-        <v>35</v>
-      </c>
-      <c r="Z3" s="4">
-        <f>(15+(15*0.4))/2</f>
-        <v>10.5</v>
-      </c>
-      <c r="AA3" s="4">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="AB3" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="4">
-        <v>0</v>
-      </c>
-      <c r="AD3" s="4">
-        <v>0</v>
-      </c>
-      <c r="AE3" s="4">
-        <v>0</v>
-      </c>
-      <c r="AF3" s="4">
-        <v>0</v>
-      </c>
-      <c r="AG3" s="4">
-        <v>0</v>
-      </c>
-      <c r="AH3" s="4">
-        <v>0</v>
-      </c>
-      <c r="AI3" s="4">
-        <v>302.25</v>
-      </c>
-      <c r="AJ3" s="4">
-        <v>604.5</v>
-      </c>
-      <c r="AK3" s="4">
-        <v>4.2622450000000001</v>
-      </c>
-      <c r="AL3" s="4">
-        <v>1</v>
-      </c>
-      <c r="AM3" s="4">
-        <v>35</v>
-      </c>
-      <c r="AN3" s="4">
-        <v>10.5</v>
-      </c>
-      <c r="AO3" s="4">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="AP3" s="4">
-        <v>0</v>
-      </c>
-      <c r="AQ3" s="4">
-        <v>0</v>
-      </c>
-      <c r="AR3" s="4">
-        <v>0</v>
-      </c>
-      <c r="AS3" s="4">
-        <v>0</v>
-      </c>
-      <c r="AT3" s="4">
-        <v>0</v>
-      </c>
-      <c r="AU3" s="4">
-        <v>0</v>
-      </c>
-      <c r="AV3" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.77</v>
-      </c>
-      <c r="E4" s="4">
-        <v>0.8</v>
-      </c>
-      <c r="F4" s="4">
-        <v>160</v>
-      </c>
-      <c r="G4" s="4">
-        <v>15</v>
-      </c>
-      <c r="H4" s="4">
-        <f t="shared" si="0"/>
-        <v>10.666666666666666</v>
-      </c>
-      <c r="I4" s="4">
-        <f>0.25*PI()*(G4)^2</f>
-        <v>176.71458676442586</v>
-      </c>
-      <c r="J4" s="4">
-        <v>0</v>
-      </c>
-      <c r="K4" s="4">
-        <f>PI()*G4*F4</f>
-        <v>7539.8223686155034</v>
-      </c>
-      <c r="L4" s="4">
-        <v>1</v>
-      </c>
-      <c r="M4" s="4">
-        <v>1</v>
-      </c>
-      <c r="N4" s="4">
-        <v>826</v>
-      </c>
-      <c r="O4" s="4">
-        <v>1652</v>
-      </c>
-      <c r="P4" s="4">
-        <v>10.54</v>
-      </c>
-      <c r="Q4" s="4">
-        <v>0.33</v>
-      </c>
-      <c r="R4" s="4">
-        <v>24.5</v>
-      </c>
-      <c r="S4" s="4">
-        <v>24.5</v>
-      </c>
-      <c r="T4" s="4">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="U4" s="4">
-        <v>300</v>
-      </c>
-      <c r="V4" s="4">
-        <v>600</v>
-      </c>
-      <c r="W4" s="4">
-        <v>5</v>
-      </c>
-      <c r="X4" s="4">
-        <v>0.3</v>
-      </c>
-      <c r="Y4" s="4">
-        <v>25</v>
-      </c>
-      <c r="Z4" s="4">
-        <v>6</v>
-      </c>
-      <c r="AA4" s="4">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="AB4" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="4">
-        <v>0</v>
-      </c>
-      <c r="AD4" s="4">
-        <v>0</v>
-      </c>
-      <c r="AE4" s="4">
-        <v>0</v>
-      </c>
-      <c r="AF4" s="4">
-        <v>0</v>
-      </c>
-      <c r="AG4" s="4">
-        <v>0</v>
-      </c>
-      <c r="AH4" s="4">
-        <v>0</v>
-      </c>
-      <c r="AI4" s="4">
-        <v>230</v>
-      </c>
-      <c r="AJ4" s="4">
-        <v>465</v>
-      </c>
-      <c r="AK4" s="4">
-        <v>1.8</v>
-      </c>
-      <c r="AL4" s="4">
-        <v>0.3</v>
-      </c>
-      <c r="AM4" s="4">
-        <v>33</v>
-      </c>
-      <c r="AN4" s="4">
-        <v>10.5</v>
-      </c>
-      <c r="AO4" s="4">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="AP4" s="4">
-        <v>0</v>
-      </c>
-      <c r="AQ4" s="4">
-        <v>0</v>
-      </c>
-      <c r="AR4" s="4">
-        <v>0</v>
-      </c>
-      <c r="AS4" s="4">
-        <v>0</v>
-      </c>
-      <c r="AT4" s="4">
-        <v>0</v>
-      </c>
-      <c r="AU4" s="4">
-        <v>0</v>
-      </c>
-      <c r="AV4" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:48" s="21" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="13" spans="1:48" s="21" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -3795,7 +3483,7 @@
           <x14:formula1>
             <xm:f>Lists!$B$2:$B$19</xm:f>
           </x14:formula1>
-          <xm:sqref>B4:B14</xm:sqref>
+          <xm:sqref>B3:B12</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3805,7 +3493,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{538960B4-04F0-4DA1-BF31-3569558CC234}">
-  <dimension ref="A1:BB15"/>
+  <dimension ref="A1:BB13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="10"/>
@@ -3990,136 +3678,137 @@
     <row r="2" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="str">
         <f>Main_Input!A2</f>
-        <v>B717</v>
+        <v>MD80</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>237</v>
       </c>
       <c r="C2" s="10">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="D2" s="10">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="E2" s="10">
-        <v>-0.3805</v>
+        <v>-0.36480000000000001</v>
       </c>
       <c r="F2" s="10">
-        <v>-0.27139999999999997</v>
+        <v>-0.22969999999999999</v>
       </c>
       <c r="G2" s="10">
-        <v>-0.16750000000000001</v>
+        <v>-9.06E-2</v>
       </c>
       <c r="H2" s="10">
-        <v>-5.4300000000000001E-2</v>
+        <v>9.1499999999999998E-2</v>
       </c>
       <c r="I2" s="10">
-        <v>5.9799999999999999E-2</v>
-      </c>
-      <c r="J2">
-        <v>0.17460000000000001</v>
-      </c>
-      <c r="K2">
-        <v>0.28949999999999998</v>
-      </c>
-      <c r="L2">
-        <v>0.40339999999999998</v>
-      </c>
-      <c r="M2">
-        <v>0.51529999999999998</v>
-      </c>
-      <c r="N2">
-        <v>0.61850000000000005</v>
-      </c>
-      <c r="O2">
-        <v>0.70960000000000001</v>
-      </c>
-      <c r="P2">
-        <v>0.80979999999999996</v>
-      </c>
-      <c r="Q2">
-        <v>0.90339999999999998</v>
+        <v>0.25209999999999999</v>
+      </c>
+      <c r="J2" s="10">
+        <v>0.3926</v>
+      </c>
+      <c r="K2" s="10">
+        <v>0.4924</v>
+      </c>
+      <c r="L2" s="10">
+        <v>0.59919999999999995</v>
+      </c>
+      <c r="M2" s="10">
+        <v>0.70809999999999995</v>
+      </c>
+      <c r="N2" s="10">
+        <v>0.81489999999999996</v>
+      </c>
+      <c r="O2" s="10">
+        <v>0.92130000000000001</v>
+      </c>
+      <c r="P2" s="10">
+        <v>1.0299</v>
+      </c>
+      <c r="Q2" s="10">
+        <v>1.1337999999999999</v>
       </c>
       <c r="R2" s="10">
-        <v>0.99139999999999995</v>
-      </c>
-      <c r="S2">
-        <v>1.0817000000000001</v>
-      </c>
-      <c r="T2">
-        <v>1.1456999999999999</v>
+        <v>1.2350000000000001</v>
+      </c>
+      <c r="S2" s="10">
+        <v>1.3317000000000001</v>
+      </c>
+      <c r="T2" s="10">
+        <v>1.4271</v>
       </c>
       <c r="U2" s="10">
-        <v>1.2031000000000001</v>
-      </c>
-      <c r="V2">
-        <v>1.2484999999999999</v>
+        <v>1.5059</v>
+      </c>
+      <c r="V2" s="10">
+        <v>1.5843</v>
       </c>
       <c r="W2" s="10">
-        <v>1.2875000000000001</v>
-      </c>
-      <c r="X2">
-        <v>9.41E-3</v>
-      </c>
-      <c r="Y2">
-        <v>8.5000000000000006E-3</v>
-      </c>
-      <c r="Z2">
-        <v>6.0099999999999997E-3</v>
-      </c>
-      <c r="AA2">
-        <v>5.6499999999999996E-3</v>
-      </c>
-      <c r="AB2">
-        <v>5.5599999999999998E-3</v>
-      </c>
-      <c r="AC2">
-        <v>5.5900000000000004E-3</v>
-      </c>
-      <c r="AD2">
-        <v>5.6600000000000001E-3</v>
-      </c>
-      <c r="AE2">
-        <v>5.79E-3</v>
-      </c>
-      <c r="AF2">
-        <v>6.0800000000000003E-3</v>
-      </c>
-      <c r="AG2">
-        <v>7.3899999999999999E-3</v>
-      </c>
-      <c r="AH2">
-        <v>1.013E-2</v>
-      </c>
-      <c r="AI2">
-        <v>1.136E-2</v>
-      </c>
-      <c r="AJ2">
-        <v>1.268E-2</v>
+        <v>1.5843</v>
+      </c>
+      <c r="X2" s="10">
+        <v>1.2370000000000001E-2</v>
+      </c>
+      <c r="Y2" s="10">
+        <v>1.1509999999999999E-2</v>
+      </c>
+      <c r="Z2" s="10">
+        <v>1.082E-2</v>
+      </c>
+      <c r="AA2" s="10">
+        <v>9.1400000000000006E-3</v>
+      </c>
+      <c r="AB2" s="10">
+        <v>6.3699999999999998E-3</v>
+      </c>
+      <c r="AC2" s="10">
+        <v>8.1300000000000001E-3</v>
+      </c>
+      <c r="AD2" s="10">
+        <v>1.027E-2</v>
+      </c>
+      <c r="AE2" s="10">
+        <v>1.1220000000000001E-2</v>
+      </c>
+      <c r="AF2" s="10">
+        <v>1.2160000000000001E-2</v>
+      </c>
+      <c r="AG2" s="10">
+        <v>1.312E-2</v>
+      </c>
+      <c r="AH2" s="10">
+        <v>1.4200000000000001E-2</v>
+      </c>
+      <c r="AI2" s="10">
+        <v>1.5100000000000001E-2</v>
+      </c>
+      <c r="AJ2" s="10">
+        <v>1.651E-2</v>
       </c>
       <c r="AK2" s="10">
-        <v>1.4630000000000001E-2</v>
-      </c>
-      <c r="AL2">
-        <v>1.6660000000000001E-2</v>
-      </c>
-      <c r="AM2">
-        <v>2.0740000000000001E-2</v>
-      </c>
-      <c r="AN2">
-        <v>2.4039999999999999E-2</v>
-      </c>
-      <c r="AO2">
-        <v>2.8039999999999999E-2</v>
+        <v>1.806E-2</v>
+      </c>
+      <c r="AL2" s="10">
+        <v>1.9970000000000002E-2</v>
+      </c>
+      <c r="AM2" s="10">
+        <v>2.1649999999999999E-2</v>
+      </c>
+      <c r="AN2" s="10">
+        <v>2.487E-2</v>
+      </c>
+      <c r="AO2" s="10">
+        <v>2.726E-2</v>
       </c>
       <c r="AP2" s="10">
-        <v>5.5599999999999998E-3</v>
+        <f>MIN(X2:AO2)</f>
+        <v>6.3699999999999998E-3</v>
       </c>
       <c r="AQ2" s="10" t="s">
         <v>238</v>
       </c>
       <c r="AR2" s="10">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="AS2" s="10">
         <v>0.3</v>
@@ -4134,10 +3823,10 @@
         <v>0</v>
       </c>
       <c r="AW2" s="10" t="s">
-        <v>238</v>
+        <v>180</v>
       </c>
       <c r="AX2" s="10">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="AY2" s="10">
         <v>0.3</v>
@@ -4152,339 +3841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:54" x14ac:dyDescent="0.2">
-      <c r="A3" s="10" t="str">
-        <f>Main_Input!A3</f>
-        <v>MD80</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="C3" s="10">
-        <v>0.11</v>
-      </c>
-      <c r="D3" s="10">
-        <v>0.36</v>
-      </c>
-      <c r="E3" s="10">
-        <v>-0.36480000000000001</v>
-      </c>
-      <c r="F3" s="10">
-        <v>-0.22969999999999999</v>
-      </c>
-      <c r="G3" s="10">
-        <v>-9.06E-2</v>
-      </c>
-      <c r="H3" s="10">
-        <v>9.1499999999999998E-2</v>
-      </c>
-      <c r="I3" s="10">
-        <v>0.25209999999999999</v>
-      </c>
-      <c r="J3" s="10">
-        <v>0.3926</v>
-      </c>
-      <c r="K3" s="10">
-        <v>0.4924</v>
-      </c>
-      <c r="L3" s="10">
-        <v>0.59919999999999995</v>
-      </c>
-      <c r="M3" s="10">
-        <v>0.70809999999999995</v>
-      </c>
-      <c r="N3" s="10">
-        <v>0.81489999999999996</v>
-      </c>
-      <c r="O3" s="10">
-        <v>0.92130000000000001</v>
-      </c>
-      <c r="P3" s="10">
-        <v>1.0299</v>
-      </c>
-      <c r="Q3" s="10">
-        <v>1.1337999999999999</v>
-      </c>
-      <c r="R3" s="10">
-        <v>1.2350000000000001</v>
-      </c>
-      <c r="S3" s="10">
-        <v>1.3317000000000001</v>
-      </c>
-      <c r="T3" s="10">
-        <v>1.4271</v>
-      </c>
-      <c r="U3" s="10">
-        <v>1.5059</v>
-      </c>
-      <c r="V3" s="10">
-        <v>1.5843</v>
-      </c>
-      <c r="W3" s="10">
-        <v>1.5843</v>
-      </c>
-      <c r="X3" s="10">
-        <v>1.2370000000000001E-2</v>
-      </c>
-      <c r="Y3" s="10">
-        <v>1.1509999999999999E-2</v>
-      </c>
-      <c r="Z3" s="10">
-        <v>1.082E-2</v>
-      </c>
-      <c r="AA3" s="10">
-        <v>9.1400000000000006E-3</v>
-      </c>
-      <c r="AB3" s="10">
-        <v>6.3699999999999998E-3</v>
-      </c>
-      <c r="AC3" s="10">
-        <v>8.1300000000000001E-3</v>
-      </c>
-      <c r="AD3" s="10">
-        <v>1.027E-2</v>
-      </c>
-      <c r="AE3" s="10">
-        <v>1.1220000000000001E-2</v>
-      </c>
-      <c r="AF3" s="10">
-        <v>1.2160000000000001E-2</v>
-      </c>
-      <c r="AG3" s="10">
-        <v>1.312E-2</v>
-      </c>
-      <c r="AH3" s="10">
-        <v>1.4200000000000001E-2</v>
-      </c>
-      <c r="AI3" s="10">
-        <v>1.5100000000000001E-2</v>
-      </c>
-      <c r="AJ3" s="10">
-        <v>1.651E-2</v>
-      </c>
-      <c r="AK3" s="10">
-        <v>1.806E-2</v>
-      </c>
-      <c r="AL3" s="10">
-        <v>1.9970000000000002E-2</v>
-      </c>
-      <c r="AM3" s="10">
-        <v>2.1649999999999999E-2</v>
-      </c>
-      <c r="AN3" s="10">
-        <v>2.487E-2</v>
-      </c>
-      <c r="AO3" s="10">
-        <v>2.726E-2</v>
-      </c>
-      <c r="AP3" s="10">
-        <f>MIN(X3:AO3)</f>
-        <v>6.3699999999999998E-3</v>
-      </c>
-      <c r="AQ3" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="AR3" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="AS3" s="10">
-        <v>0.3</v>
-      </c>
-      <c r="AT3" s="10">
-        <v>0</v>
-      </c>
-      <c r="AU3" s="10">
-        <v>0</v>
-      </c>
-      <c r="AV3" s="10">
-        <v>0</v>
-      </c>
-      <c r="AW3" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="AX3" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="AY3" s="10">
-        <v>0.3</v>
-      </c>
-      <c r="AZ3" s="10">
-        <v>0</v>
-      </c>
-      <c r="BA3" s="10">
-        <v>0</v>
-      </c>
-      <c r="BB3" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:54" x14ac:dyDescent="0.2">
-      <c r="A4" s="10" t="str">
-        <f>Main_Input!A4</f>
-        <v>BuffAir</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="C4" s="10">
-        <v>0.11</v>
-      </c>
-      <c r="D4" s="10">
-        <v>0.36</v>
-      </c>
-      <c r="E4" s="10">
-        <v>-0.36480000000000001</v>
-      </c>
-      <c r="F4" s="10">
-        <v>-0.22969999999999999</v>
-      </c>
-      <c r="G4" s="10">
-        <v>-9.06E-2</v>
-      </c>
-      <c r="H4" s="10">
-        <v>9.1499999999999998E-2</v>
-      </c>
-      <c r="I4" s="10">
-        <v>0.25209999999999999</v>
-      </c>
-      <c r="J4" s="10">
-        <v>0.3926</v>
-      </c>
-      <c r="K4" s="10">
-        <v>0.4924</v>
-      </c>
-      <c r="L4" s="10">
-        <v>0.59919999999999995</v>
-      </c>
-      <c r="M4" s="10">
-        <v>0.70809999999999995</v>
-      </c>
-      <c r="N4" s="10">
-        <v>0.81489999999999996</v>
-      </c>
-      <c r="O4" s="10">
-        <v>0.92130000000000001</v>
-      </c>
-      <c r="P4" s="10">
-        <v>1.0299</v>
-      </c>
-      <c r="Q4" s="10">
-        <v>1.1337999999999999</v>
-      </c>
-      <c r="R4" s="10">
-        <v>1.2350000000000001</v>
-      </c>
-      <c r="S4" s="10">
-        <v>1.3317000000000001</v>
-      </c>
-      <c r="T4" s="10">
-        <v>1.4271</v>
-      </c>
-      <c r="U4" s="10">
-        <v>1.5059</v>
-      </c>
-      <c r="V4" s="10">
-        <v>1.5843</v>
-      </c>
-      <c r="W4" s="10">
-        <v>1.5843</v>
-      </c>
-      <c r="X4" s="10">
-        <v>1.2370000000000001E-2</v>
-      </c>
-      <c r="Y4" s="10">
-        <v>1.1509999999999999E-2</v>
-      </c>
-      <c r="Z4" s="10">
-        <v>1.082E-2</v>
-      </c>
-      <c r="AA4" s="10">
-        <v>9.1400000000000006E-3</v>
-      </c>
-      <c r="AB4" s="10">
-        <v>6.3699999999999998E-3</v>
-      </c>
-      <c r="AC4" s="10">
-        <v>8.1300000000000001E-3</v>
-      </c>
-      <c r="AD4" s="10">
-        <v>1.027E-2</v>
-      </c>
-      <c r="AE4" s="10">
-        <v>1.1220000000000001E-2</v>
-      </c>
-      <c r="AF4" s="10">
-        <v>1.2160000000000001E-2</v>
-      </c>
-      <c r="AG4" s="10">
-        <v>1.312E-2</v>
-      </c>
-      <c r="AH4" s="10">
-        <v>1.4200000000000001E-2</v>
-      </c>
-      <c r="AI4" s="10">
-        <v>1.5100000000000001E-2</v>
-      </c>
-      <c r="AJ4" s="10">
-        <v>1.651E-2</v>
-      </c>
-      <c r="AK4" s="10">
-        <v>1.806E-2</v>
-      </c>
-      <c r="AL4" s="10">
-        <v>1.9970000000000002E-2</v>
-      </c>
-      <c r="AM4" s="10">
-        <v>2.1649999999999999E-2</v>
-      </c>
-      <c r="AN4" s="10">
-        <v>2.487E-2</v>
-      </c>
-      <c r="AO4" s="10">
-        <v>2.726E-2</v>
-      </c>
-      <c r="AP4" s="10">
-        <f>MIN(X4:AO4)</f>
-        <v>6.3699999999999998E-3</v>
-      </c>
-      <c r="AQ4" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="AR4" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="AS4" s="10">
-        <v>0.3</v>
-      </c>
-      <c r="AT4" s="10">
-        <v>0</v>
-      </c>
-      <c r="AU4" s="10">
-        <v>0</v>
-      </c>
-      <c r="AV4" s="10">
-        <v>0</v>
-      </c>
-      <c r="AW4" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="AX4" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="AY4" s="10">
-        <v>0.3</v>
-      </c>
-      <c r="AZ4" s="10">
-        <v>0</v>
-      </c>
-      <c r="BA4" s="10">
-        <v>0</v>
-      </c>
-      <c r="BB4" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:54" s="22" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="13" spans="1:54" s="22" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4493,7 +3850,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B77D4EB-A9CB-4E6A-B1A1-7AF90F186000}">
-  <dimension ref="A1:R15"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="21.5" customWidth="1"/>
@@ -4563,10 +3920,10 @@
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" t="str">
         <f>Main_Input!A2</f>
-        <v>B717</v>
+        <v>MD80</v>
       </c>
       <c r="B2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C2">
         <v>2</v>
@@ -4575,7 +3932,7 @@
         <v>19500</v>
       </c>
       <c r="E2">
-        <v>0.37</v>
+        <v>0.73</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -4584,7 +3941,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4618,123 +3975,9 @@
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A3" t="str">
-        <f>Main_Input!A3</f>
-        <v>MD80</v>
-      </c>
-      <c r="B3" t="s">
-        <v>185</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>19500</v>
-      </c>
-      <c r="E3">
-        <v>0.73</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0.2</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A4" t="str">
-        <f>Main_Input!A4</f>
-        <v>BuffAir</v>
-      </c>
-      <c r="B4" t="s">
-        <v>185</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>19500</v>
-      </c>
-      <c r="E4">
-        <v>0.73</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0.2</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="H5" s="29"/>
-    </row>
-    <row r="15" spans="1:18" s="20" customFormat="1" x14ac:dyDescent="0.2"/>
+      <c r="H3" s="29"/>
+    </row>
+    <row r="13" spans="1:18" s="20" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -4745,7 +3988,7 @@
           <x14:formula1>
             <xm:f>Lists!$A$2:$A$7</xm:f>
           </x14:formula1>
-          <xm:sqref>B3:B14</xm:sqref>
+          <xm:sqref>B2:B12</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
